--- a/data/batches/B04_Interventions/Test_Validation_Report/Test_Validation_Report_B04.xlsx
+++ b/data/batches/B04_Interventions/Test_Validation_Report/Test_Validation_Report_B04.xlsx
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=72</t>
+          <t>Complete Row @ CSV Row 959; count=1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=77</t>
+          <t>Complete Row @ CSV Row 959; count=2</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -10660,17 +10660,17 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=72</t>
+          <t>Complete Row @ CSV Row 969; count=1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=77</t>
+          <t>Complete Row @ CSV Row 969; count=2</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -10743,17 +10743,17 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-USA_SITE04-0016; count=68</t>
+          <t>Complete Row @ CSV Row 1570; count=1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-USA_SITE04-0016; count=70</t>
+          <t>Complete Row @ CSV Row 1570; count=2</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -10826,17 +10826,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=72</t>
+          <t>Complete Row @ CSV Row 961; count=1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=77</t>
+          <t>Complete Row @ CSV Row 961; count=2</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -10909,17 +10909,17 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-USA_SITE04-0016; count=68</t>
+          <t>Complete Row @ CSV Row 1528; count=1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-USA_SITE04-0016; count=70</t>
+          <t>Complete Row @ CSV Row 1528; count=2</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -10992,17 +10992,17 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=72</t>
+          <t>Complete Row @ CSV Row 980; count=1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=77</t>
+          <t>Complete Row @ CSV Row 980; count=2</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -11075,17 +11075,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=72</t>
+          <t>Complete Row @ CSV Row 940; count=1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -11143,12 +11143,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>USUBJID=GB001-2001-POL_SITE01-0004; count=77</t>
+          <t>Complete Row @ CSV Row 940; count=2</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -13737,11 +13737,7 @@
           <t>DV</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>DVCAT</t>
@@ -13749,25 +13745,49 @@
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -14640,10 +14660,10 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -14658,7 +14678,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
